--- a/data/trans_orig/IP2001-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP2001-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14318</t>
+          <t>15093</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88784</t>
+          <t>88352</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95098</t>
+          <t>95159</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80811</t>
+          <t>81207</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88849</t>
+          <t>88889</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173731</t>
+          <t>172956</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>182958</t>
+          <t>182794</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>691</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13985</t>
+          <t>14002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73777</t>
+          <t>74290</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80352</t>
+          <t>80355</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72026</t>
+          <t>72271</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79676</t>
+          <t>79766</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>149446</t>
+          <t>149429</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158825</t>
+          <t>158793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10406</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16081</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52883</t>
+          <t>53587</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60912</t>
+          <t>60724</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88745</t>
+          <t>88844</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95922</t>
+          <t>95895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145029</t>
+          <t>144830</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155612</t>
+          <t>155359</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11925</t>
+          <t>12270</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24862</t>
+          <t>24850</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12821</t>
+          <t>13325</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26946</t>
+          <t>27108</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28757</t>
+          <t>28068</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46315</t>
+          <t>46755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166802</t>
+          <t>166814</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>179739</t>
+          <t>179394</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>159269</t>
+          <t>159107</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>173394</t>
+          <t>172890</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>331564</t>
+          <t>331124</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>349122</t>
+          <t>349811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17761</t>
+          <t>18555</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18532</t>
+          <t>18610</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17678</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31815</t>
+          <t>32800</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81794</t>
+          <t>81000</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92024</t>
+          <t>92168</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99908</t>
+          <t>99830</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110565</t>
+          <t>110923</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186180</t>
+          <t>185195</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>200317</t>
+          <t>200156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64100</t>
+          <t>64604</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70271</t>
+          <t>70301</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61108</t>
+          <t>60449</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127421</t>
+          <t>127800</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>134508</t>
+          <t>134600</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34879</t>
+          <t>34878</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56649</t>
+          <t>56454</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>39571</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59644</t>
+          <t>61459</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79622</t>
+          <t>78403</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>109168</t>
+          <t>108127</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>546821</t>
+          <t>547016</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>568591</t>
+          <t>568592</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>581905</t>
+          <t>580090</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>603002</t>
+          <t>601978</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1135851</t>
+          <t>1136892</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1165397</t>
+          <t>1166616</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>10487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74978</t>
+          <t>75290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81759</t>
+          <t>81893</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77139</t>
+          <t>77220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154482</t>
+          <t>154745</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162856</t>
+          <t>162585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>11536</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>6198</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16867</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74948</t>
+          <t>75210</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83559</t>
+          <t>83848</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84199</t>
+          <t>84206</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90762</t>
+          <t>90222</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>161953</t>
+          <t>162523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172666</t>
+          <t>172622</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15704</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,47 +4104,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>15,54%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>18246</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>12402</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>25676</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>11,19%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>7,61%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>15,75%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>18246</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>12505</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>25350</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>11,19%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65042</t>
+          <t>64352</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74491</t>
+          <t>74464</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69308</t>
+          <t>69474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77550</t>
+          <t>77969</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,47 +4217,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>84,46%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>94,78%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>144760</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>137330</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>150604</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>88,81%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>84,25%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>94,27%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>144760</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>137656</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>150501</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>88,81%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>84,45%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25358</t>
+          <t>24047</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>10476</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>23931</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25948</t>
+          <t>26460</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44571</t>
+          <t>45501</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164987</t>
+          <t>166298</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177978</t>
+          <t>178949</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186770</t>
+          <t>186691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>200108</t>
+          <t>200146</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>356396</t>
+          <t>355466</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>375019</t>
+          <t>374507</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25153</t>
+          <t>24861</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,82 +4755,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>18,29%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>20024</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>13689</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>28355</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>10,46%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>21,66%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>38089</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>29681</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>49371</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>14,27%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>11,12%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>18,5%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20024</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>13621</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>27965</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>15,3%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>10,4%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>21,36%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>38089</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>29375</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>47862</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>14,27%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110787</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123854</t>
+          <t>123609</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,82 +4868,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>81,71%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,93%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>110889</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>102558</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>117224</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>84,7%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>78,34%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>89,54%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>228764</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>217482</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>237172</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>85,73%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>81,5%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,11%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>110889</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>102948</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>117292</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>84,7%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>78,64%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>89,6%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>228764</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>218991</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>237478</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>85,73%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>82,06%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,88%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13625</t>
+          <t>13358</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>15548</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45129</t>
+          <t>44509</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53874</t>
+          <t>54141</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63166</t>
+          <t>62877</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>100758</t>
+          <t>101213</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111203</t>
+          <t>111357</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47404</t>
+          <t>45977</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71340</t>
+          <t>69901</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47422</t>
+          <t>47139</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72645</t>
+          <t>70518</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98537</t>
+          <t>99347</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133788</t>
+          <t>133515</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>555033</t>
+          <t>556472</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>578969</t>
+          <t>580396</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>592620</t>
+          <t>594747</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>617843</t>
+          <t>618126</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1157851</t>
+          <t>1158124</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1193102</t>
+          <t>1192292</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13982</t>
+          <t>13432</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8959</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22471</t>
+          <t>21553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65653</t>
+          <t>65724</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74202</t>
+          <t>74530</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76164</t>
+          <t>76714</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85914</t>
+          <t>86188</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144930</t>
+          <t>145848</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158442</t>
+          <t>158265</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12317</t>
+          <t>13136</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12974</t>
+          <t>12672</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10371</t>
+          <t>10066</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22967</t>
+          <t>22393</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85354</t>
+          <t>84535</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93757</t>
+          <t>93369</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92553</t>
+          <t>92855</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>101332</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>180231</t>
+          <t>180805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>192827</t>
+          <t>193132</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>14070</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50393</t>
+          <t>50314</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56696</t>
+          <t>56657</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62462</t>
+          <t>62030</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69411</t>
+          <t>68862</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115681</t>
+          <t>115231</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124829</t>
+          <t>124779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20981</t>
+          <t>20620</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35914</t>
+          <t>37003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14744</t>
+          <t>14803</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29364</t>
+          <t>29262</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>40316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60287</t>
+          <t>62642</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171851</t>
+          <t>170762</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186784</t>
+          <t>187145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173125</t>
+          <t>173227</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>187745</t>
+          <t>187686</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>349967</t>
+          <t>347612</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>371669</t>
+          <t>369938</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,17%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23437</t>
+          <t>22773</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15490</t>
+          <t>15554</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30362</t>
+          <t>30171</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29280</t>
+          <t>28129</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48517</t>
+          <t>47835</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106984</t>
+          <t>107648</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119724</t>
+          <t>119422</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>104079</t>
+          <t>104270</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>118951</t>
+          <t>118887</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216344</t>
+          <t>217026</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>235581</t>
+          <t>236732</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>565</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50173</t>
+          <t>50003</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55494</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59858</t>
+          <t>59769</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64452</t>
+          <t>64449</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111570</t>
+          <t>111298</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>119214</t>
+          <t>119253</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54373</t>
+          <t>54181</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79467</t>
+          <t>78750</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53125</t>
+          <t>53596</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78278</t>
+          <t>78633</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>114478</t>
+          <t>113883</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>150783</t>
+          <t>148752</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>548811</t>
+          <t>549528</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>573905</t>
+          <t>574097</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>590148</t>
+          <t>589793</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>615301</t>
+          <t>614830</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1145922</t>
+          <t>1147953</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1182227</t>
+          <t>1182822</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20190</t>
+          <t>19982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92406</t>
+          <t>92945</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100128</t>
+          <t>99912</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>122902</t>
+          <t>122997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132307</t>
+          <t>132596</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>218766</t>
+          <t>218974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>230740</t>
+          <t>230428</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14565</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89280</t>
+          <t>90042</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81524</t>
+          <t>80305</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90859</t>
+          <t>90701</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173362</t>
+          <t>174137</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184555</t>
+          <t>184517</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>10334</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>42642</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48620</t>
+          <t>48375</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57578</t>
+          <t>57122</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103982</t>
+          <t>102728</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111140</t>
+          <t>110912</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17875</t>
+          <t>17270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9357</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23505</t>
+          <t>23319</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>17400</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36261</t>
+          <t>36840</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>196091</t>
+          <t>196696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>207894</t>
+          <t>208350</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>187620</t>
+          <t>187806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201768</t>
+          <t>201593</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>388830</t>
+          <t>388251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>407075</t>
+          <t>407691</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10064</t>
+          <t>10033</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16736</t>
+          <t>16843</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>8529</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>22786</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106542</t>
+          <t>106573</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114400</t>
+          <t>114525</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142804</t>
+          <t>142697</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154581</t>
+          <t>154801</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>252914</t>
+          <t>253360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>267391</t>
+          <t>267617</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>501</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8559</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63884</t>
+          <t>64247</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61895</t>
+          <t>61209</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69961</t>
+          <t>69953</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>129837</t>
+          <t>129188</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>138025</t>
+          <t>137766</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19879</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37163</t>
+          <t>37938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31907</t>
+          <t>31290</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54798</t>
+          <t>57353</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55536</t>
+          <t>55902</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87740</t>
+          <t>87706</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>609748</t>
+          <t>608973</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>627032</t>
+          <t>626718</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>678820</t>
+          <t>676265</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>701711</t>
+          <t>702328</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1292790</t>
+          <t>1292824</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1324994</t>
+          <t>1324628</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
